--- a/apps/web-ele/public/example/範例-人員名單.xlsx
+++ b/apps/web-ele/public/example/範例-人員名單.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Applications/XAMPP/xamppfiles/htdocs/project_development/workcloud/public/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\edm\apps\web-ele\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC66C128-795C-7C44-9B17-16AE5F6309DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD6DF1E-AE93-411D-B726-AA33A6B449B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{740A64DE-792B-F94E-AC89-0D860BFB4FC8}"/>
+    <workbookView xWindow="59250" yWindow="1650" windowWidth="21600" windowHeight="11175" xr2:uid="{740A64DE-792B-F94E-AC89-0D860BFB4FC8}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,11 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="62">
-  <si>
-    <t>身分證字號</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
   <si>
     <t>行動電話</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -127,26 +123,6 @@
   </si>
   <si>
     <t>資深協理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A111111111</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A222222222</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A333333333</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A444444444</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A555555555</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -274,7 +250,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -670,30 +646,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E06DC15-A556-954D-BB74-08508EBA4085}">
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11" style="1" customWidth="1"/>
-    <col min="7" max="8" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="1"/>
-    <col min="10" max="10" width="13.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="10.83203125" style="1"/>
-    <col min="15" max="15" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="7" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.81640625" style="1"/>
+    <col min="9" max="9" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="10.81640625" style="1"/>
+    <col min="14" max="14" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="10.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="20">
+    <row r="1" spans="1:15" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -711,45 +686,42 @@
         <v>4</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>20</v>
@@ -758,201 +730,189 @@
         <v>21</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="M4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L4" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="L5" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O5" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>21</v>
@@ -961,31 +921,28 @@
         <v>22</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="M6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="N6" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="O6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/apps/web-ele/public/example/範例-人員名單.xlsx
+++ b/apps/web-ele/public/example/範例-人員名單.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\edm\apps\web-ele\public\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD6DF1E-AE93-411D-B726-AA33A6B449B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9921ACD6-AACF-4C56-9370-06D549A948A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59250" yWindow="1650" windowWidth="21600" windowHeight="11175" xr2:uid="{740A64DE-792B-F94E-AC89-0D860BFB4FC8}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{740A64DE-792B-F94E-AC89-0D860BFB4FC8}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="60">
   <si>
     <t>行動電話</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -243,6 +243,22 @@
   </si>
   <si>
     <t>公司所在國家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>業務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HW-U03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HW-O68</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HW-Q78</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -646,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E06DC15-A556-954D-BB74-08508EBA4085}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
@@ -659,11 +675,11 @@
     <col min="9" max="9" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="13" width="10.81640625" style="1"/>
     <col min="14" max="14" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="10.81640625" style="1"/>
+    <col min="15" max="16" width="14.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="10.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>26</v>
       </c>
@@ -709,8 +725,11 @@
       <c r="O1" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="P1" s="3" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -756,8 +775,11 @@
       <c r="O2" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="P2" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -803,8 +825,11 @@
       <c r="O3" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="P3" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -850,8 +875,11 @@
       <c r="O4" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="P4" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -897,8 +925,11 @@
       <c r="O5" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="P5" s="1" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -943,6 +974,9 @@
       </c>
       <c r="O6" s="1" t="s">
         <v>48</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
